--- a/Gastos.xlsx
+++ b/Gastos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enero" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diciembre" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -58,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -355,10 +356,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="3">
+    <row r="1" s="3">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -384,8 +385,108 @@
           <t>Cuotas pendientes</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1" s="3"/>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comida</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Expensas</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Ahorros</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="F2">
+        <f>SUMIF(B:B,F1,C:C)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIF(B:B,G1,C:C)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIF(B:B,H1,C:C)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>SUMIF(B:B,I1,C:C)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SUMIF(B:B,J1,C:C)</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIF(B:B,K1,C:C)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>SUMIF(B:B,L1,C:C)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>SUMIF(B:B,M1,C:C)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>SUMIF(B:B,N1,C:C)</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>SUMIF(B:B,O1,C:C)</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>SUMIF(B:B,P1,C:C)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -398,10 +499,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="3">
+    <row r="1" s="3">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -427,8 +528,108 @@
           <t>Cuotas pendientes</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1" s="3"/>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comida</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Expensas</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Ahorros</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="F2">
+        <f>SUMIF(B:B,F1,C:C)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIF(B:B,G1,C:C)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIF(B:B,H1,C:C)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>SUMIF(B:B,I1,C:C)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SUMIF(B:B,J1,C:C)</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIF(B:B,K1,C:C)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>SUMIF(B:B,L1,C:C)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>SUMIF(B:B,M1,C:C)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>SUMIF(B:B,N1,C:C)</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>SUMIF(B:B,O1,C:C)</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>SUMIF(B:B,P1,C:C)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -441,10 +642,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" s="3">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -470,8 +671,108 @@
           <t>Cuotas pendientes</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1" s="3"/>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comida</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Expensas</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Ahorros</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="F2">
+        <f>SUMIF(B:B,F1,C:C)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIF(B:B,G1,C:C)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIF(B:B,H1,C:C)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>SUMIF(B:B,I1,C:C)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SUMIF(B:B,J1,C:C)</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIF(B:B,K1,C:C)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>SUMIF(B:B,L1,C:C)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>SUMIF(B:B,M1,C:C)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>SUMIF(B:B,N1,C:C)</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>SUMIF(B:B,O1,C:C)</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>SUMIF(B:B,P1,C:C)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -484,10 +785,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" s="3">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -513,8 +814,108 @@
           <t>Cuotas pendientes</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1" s="3"/>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comida</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Expensas</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Ahorros</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="F2">
+        <f>SUMIF(B:B,F1,C:C)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIF(B:B,G1,C:C)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIF(B:B,H1,C:C)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>SUMIF(B:B,I1,C:C)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SUMIF(B:B,J1,C:C)</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIF(B:B,K1,C:C)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>SUMIF(B:B,L1,C:C)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>SUMIF(B:B,M1,C:C)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>SUMIF(B:B,N1,C:C)</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>SUMIF(B:B,O1,C:C)</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>SUMIF(B:B,P1,C:C)</f>
+        <v/>
+      </c>
+    </row>
     <row r="3" ht="14.25" customHeight="1" s="3"/>
     <row r="4" ht="14.25" customHeight="1" s="3"/>
   </sheetData>
@@ -529,10 +930,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" s="3">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -558,8 +959,108 @@
           <t>Cuotas pendientes</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1" s="3"/>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comida</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Expensas</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Ahorros</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="F2">
+        <f>SUMIF(B:B,F1,C:C)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIF(B:B,G1,C:C)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIF(B:B,H1,C:C)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>SUMIF(B:B,I1,C:C)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SUMIF(B:B,J1,C:C)</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIF(B:B,K1,C:C)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>SUMIF(B:B,L1,C:C)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>SUMIF(B:B,M1,C:C)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>SUMIF(B:B,N1,C:C)</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>SUMIF(B:B,O1,C:C)</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>SUMIF(B:B,P1,C:C)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -572,10 +1073,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" s="3">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -601,8 +1102,108 @@
           <t>Cuotas pendientes</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1" s="3"/>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comida</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Expensas</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Ahorros</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="F2">
+        <f>SUMIF(B:B,F1,C:C)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIF(B:B,G1,C:C)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIF(B:B,H1,C:C)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>SUMIF(B:B,I1,C:C)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SUMIF(B:B,J1,C:C)</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIF(B:B,K1,C:C)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>SUMIF(B:B,L1,C:C)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>SUMIF(B:B,M1,C:C)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>SUMIF(B:B,N1,C:C)</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>SUMIF(B:B,O1,C:C)</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>SUMIF(B:B,P1,C:C)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -615,10 +1216,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" s="3">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -644,8 +1245,108 @@
           <t>Cuotas pendientes</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1" s="3"/>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comida</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Expensas</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Ahorros</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="F2">
+        <f>SUMIF(B:B,F1,C:C)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIF(B:B,G1,C:C)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIF(B:B,H1,C:C)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>SUMIF(B:B,I1,C:C)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SUMIF(B:B,J1,C:C)</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIF(B:B,K1,C:C)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>SUMIF(B:B,L1,C:C)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>SUMIF(B:B,M1,C:C)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>SUMIF(B:B,N1,C:C)</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>SUMIF(B:B,O1,C:C)</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>SUMIF(B:B,P1,C:C)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -658,10 +1359,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" s="3">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -687,8 +1388,108 @@
           <t>Cuotas pendientes</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1" s="3"/>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comida</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Expensas</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Ahorros</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="F2">
+        <f>SUMIF(B:B,F1,C:C)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIF(B:B,G1,C:C)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIF(B:B,H1,C:C)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>SUMIF(B:B,I1,C:C)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SUMIF(B:B,J1,C:C)</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIF(B:B,K1,C:C)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>SUMIF(B:B,L1,C:C)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>SUMIF(B:B,M1,C:C)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>SUMIF(B:B,N1,C:C)</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>SUMIF(B:B,O1,C:C)</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>SUMIF(B:B,P1,C:C)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -701,10 +1502,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" s="3">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -730,8 +1531,108 @@
           <t>Cuotas pendientes</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1" s="3"/>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comida</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Expensas</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Ahorros</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="F2">
+        <f>SUMIF(B:B,F1,C:C)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIF(B:B,G1,C:C)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIF(B:B,H1,C:C)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>SUMIF(B:B,I1,C:C)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SUMIF(B:B,J1,C:C)</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIF(B:B,K1,C:C)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>SUMIF(B:B,L1,C:C)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>SUMIF(B:B,M1,C:C)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>SUMIF(B:B,N1,C:C)</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>SUMIF(B:B,O1,C:C)</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>SUMIF(B:B,P1,C:C)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -744,7 +1645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.85546875" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -780,6 +1681,61 @@
           <t>Cuotas pendientes</t>
         </is>
       </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comida</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Expensas</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Ahorros</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -805,6 +1761,50 @@
           <t>1</t>
         </is>
       </c>
+      <c r="F2">
+        <f>SUMIF(B:B,F1,C:C)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIF(B:B,G1,C:C)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIF(B:B,H1,C:C)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>SUMIF(B:B,I1,C:C)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SUMIF(B:B,J1,C:C)</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIF(B:B,K1,C:C)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>SUMIF(B:B,L1,C:C)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>SUMIF(B:B,M1,C:C)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>SUMIF(B:B,N1,C:C)</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>SUMIF(B:B,O1,C:C)</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>SUMIF(B:B,P1,C:C)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -876,6 +1876,31 @@
         </is>
       </c>
       <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -893,10 +1918,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" s="3">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -922,8 +1947,108 @@
           <t>Cuotas pendientes</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1" s="3"/>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comida</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Expensas</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Ahorros</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="F2">
+        <f>SUMIF(B:B,F1,C:C)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIF(B:B,G1,C:C)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIF(B:B,H1,C:C)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>SUMIF(B:B,I1,C:C)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SUMIF(B:B,J1,C:C)</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIF(B:B,K1,C:C)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>SUMIF(B:B,L1,C:C)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>SUMIF(B:B,M1,C:C)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>SUMIF(B:B,N1,C:C)</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>SUMIF(B:B,O1,C:C)</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>SUMIF(B:B,P1,C:C)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -936,10 +2061,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" s="3">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -965,8 +2090,108 @@
           <t>Cuotas pendientes</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="14.25" customHeight="1" s="3"/>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Comida</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Alquiler</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Expensas</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Ahorros</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="F2">
+        <f>SUMIF(B:B,F1,C:C)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>SUMIF(B:B,G1,C:C)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>SUMIF(B:B,H1,C:C)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>SUMIF(B:B,I1,C:C)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SUMIF(B:B,J1,C:C)</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>SUMIF(B:B,K1,C:C)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>SUMIF(B:B,L1,C:C)</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>SUMIF(B:B,M1,C:C)</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>SUMIF(B:B,N1,C:C)</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>SUMIF(B:B,O1,C:C)</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>SUMIF(B:B,P1,C:C)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Gastos.xlsx
+++ b/Gastos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3165" yWindow="2070" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Ahorros" sheetId="1" state="visible" r:id="rId1"/>
@@ -27,9 +27,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -62,14 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -362,10 +359,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.7109375" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
+    <col width="10.7109375" customWidth="1" style="3" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -398,138 +395,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>test1</t>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10000</v>
+        <v>23150</v>
       </c>
       <c r="C2" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
+        <v>30000</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>45520</v>
       </c>
       <c r="E2" t="n">
-        <v>10000</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>test2</t>
+          <t>testeo 2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3000</v>
+        <v>31133</v>
       </c>
       <c r="C3" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
+        <v>31333</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>45520</v>
       </c>
       <c r="E3" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>test 3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>45509</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>test 4</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>500</v>
-      </c>
-      <c r="C5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>45509</v>
-      </c>
-      <c r="E5" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>test 5</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>600</v>
-      </c>
-      <c r="C6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>45509</v>
-      </c>
-      <c r="E6" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>test 6</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>700</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7500</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>45509</v>
-      </c>
-      <c r="E7" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>test 3</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>45510</v>
-      </c>
-      <c r="E8" t="n">
-        <v>20000</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -543,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +471,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" s="4">
+    <row r="2" ht="14.25" customHeight="1" s="3">
       <c r="A2" t="inlineStr">
         <is>
           <t>2024-09-29</t>
@@ -594,6 +492,29 @@
       </c>
       <c r="E2" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20250</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>teclado keychron C1 ML</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,7 +559,29 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" s="4"/>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>20250</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>teclado keychron C1 ML</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -651,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -681,7 +624,29 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" s="4"/>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>20250</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>teclado keychron C1 ML</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -694,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -724,9 +689,33 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" s="4"/>
-    <row r="3" ht="14.25" customHeight="1" s="4"/>
-    <row r="4" ht="14.25" customHeight="1" s="4"/>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>teclado keychron C1 ML</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1" s="3"/>
+    <row r="4" ht="14.25" customHeight="1" s="3"/>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -739,7 +728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,7 +758,29 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" s="4"/>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>20250</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>teclado keychron C1 ML</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -782,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,7 +823,29 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" s="4"/>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>20250</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>teclado keychron C1 ML</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -825,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,7 +888,29 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" s="4"/>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>20250</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>teclado keychron C1 ML</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -868,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,7 +953,29 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" s="4"/>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>20250</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>teclado keychron C1 ML</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -911,7 +988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -941,7 +1018,29 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" s="4"/>
+    <row r="2" ht="14.25" customHeight="1" s="3">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>20250</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>teclado keychron C1 ML</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -954,7 +1053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1122,6 +1221,29 @@
         <is>
           <t>1</t>
         </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bolucompra</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>20250</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>teclado keychron C1 ML</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1136,14 +1258,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.7109375" customWidth="1" style="4" min="1" max="1"/>
+    <col width="10.7109375" customWidth="1" style="3" min="1" max="1"/>
     <col width="11.140625" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
     <col width="8.28515625" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
-    <col width="20.7109375" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
-    <col width="16.7109375" bestFit="1" customWidth="1" style="4" min="5" max="5"/>
+    <col width="20.7109375" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="16.7109375" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1206,7 +1328,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Agua</t>
+          <t>Luz</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1226,7 +1348,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1246,7 +1368,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Luz</t>
+          <t>Bolucompra</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1259,18 +1381,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2024-07-10</t>
-        </is>
+      <c r="A6" s="4" t="n">
+        <v>45500</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Expensas</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>2222</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1281,34 +1401,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1111</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bolucompra</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>45500</v>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Expensas</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2222</v>
+        <v>201</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1319,16 +1441,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Luz</t>
+          <t>Comida</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1111</v>
+        <v>500</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1339,16 +1461,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Comida</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>201</v>
+        <v>500</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1364,11 +1486,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Comida</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1379,16 +1501,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Comida</t>
+          <t>Bolucompra</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1399,16 +1521,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Alquiler</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>250</v>
+        <v>250000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1424,11 +1546,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bolucompra</t>
+          <t>Comida</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>45000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1444,11 +1566,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alquiler</t>
+          <t>Expensas</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>250000</v>
+        <v>32000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1464,11 +1586,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Comida</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>45000</v>
+        <v>13000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1484,11 +1606,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Expensas</t>
+          <t>Agua</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>32000</v>
+        <v>13000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1504,7 +1626,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1524,11 +1646,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Agua</t>
+          <t>Luz</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13000</v>
+        <v>38000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1544,11 +1666,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13000</v>
+        <v>6000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1564,11 +1686,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Luz</t>
+          <t>Bolucompra</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38000</v>
+        <v>8000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1584,11 +1706,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Transporte</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6000</v>
+        <v>2000</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Sube</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1599,16 +1726,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bolucompra</t>
+          <t>Agua</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1619,21 +1746,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Transporte</t>
+          <t>Ingresos</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Sube</t>
-        </is>
+        <v>324.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1644,16 +1766,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Agua</t>
+          <t>Ingresos</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>20000</v>
+        <v>324.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1673,12 +1795,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>440000</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
+        <v>324.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1689,21 +1806,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ingresos</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
+        <v>200</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1714,32 +1826,30 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ingresos</t>
+          <t>Bolucompra</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>324.5</v>
+        <v>20250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>teclado keychron C1 ML</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1748,114 +1858,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>324.5</v>
+        <v>500000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Descripcion</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Ingresos</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>324.5</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Ingresos</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>324.5</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Ingresos</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>324.5</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Ingresos</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>324.5</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1873,8 +1883,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11.5703125" customWidth="1" style="3" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1903,71 +1916,66 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" s="4">
+    <row r="2" ht="14.25" customHeight="1" s="3">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bolucompra</t>
+          <t>Transporte</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
+        <v>2000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ingresos</t>
+          <t>Bolucompra</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>500000</v>
+        <v>20250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>teclado keychron C1 ML</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ingresos</t>
+          <t>Bolucompra</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50000</v>
+        <v>635</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Trine collection para switch</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1979,20 +1987,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transporte</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2000</v>
+        <v>10153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t> </t>
+          <t>lidil cort farmacia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2004,26 +2012,88 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Luz</t>
+          <t>Bolucompra</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t> </t>
+          <t>adelanto grip 2ds Kaisa3d</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>45521</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>testeo 2</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>45521</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>testeo 2</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
